--- a/app/src/main/res/raw/household_relocation_form.xlsx
+++ b/app/src/main/res/raw/household_relocation_form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27795" windowHeight="12195" tabRatio="500"/>
+    <workbookView windowWidth="22620" windowHeight="12090" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="columns" sheetId="1" r:id="rId1"/>
@@ -490,7 +490,7 @@
     <t>repeat_name</t>
   </si>
   <si>
-    <t>xml_node_name</t>
+    <t>repeat_xml_node</t>
   </si>
   <si>
     <t>rawHouseholdRelocation</t>
@@ -513,10 +513,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -550,15 +550,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -572,7 +566,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -580,7 +574,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -595,7 +589,30 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -611,7 +628,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -624,16 +663,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -641,14 +673,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -662,30 +687,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Arial"/>
@@ -693,9 +694,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -733,181 +733,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -994,6 +994,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1024,32 +1048,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1067,9 +1065,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1085,152 +1085,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1301,7 +1301,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1725,7 +1724,7 @@
       <c r="I2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="17" t="s">
         <v>23</v>
       </c>
       <c r="K2" s="4" t="s">
@@ -1759,7 +1758,7 @@
       <c r="I3" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="J3" s="17" t="s">
         <v>28</v>
       </c>
       <c r="K3" s="4" t="s">
@@ -1793,7 +1792,7 @@
       <c r="I4" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="17" t="s">
         <v>33</v>
       </c>
       <c r="K4" s="4" t="s">
@@ -1825,14 +1824,14 @@
       <c r="I5" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="30" t="s">
+      <c r="J5" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="31" t="s">
+      <c r="K5" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
       <c r="O5" t="b">
         <v>1</v>
       </c>
@@ -1853,14 +1852,14 @@
       <c r="I6" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="31" t="s">
+      <c r="K6" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
       <c r="O6" t="b">
         <v>1</v>
       </c>
@@ -1879,14 +1878,14 @@
       <c r="I7" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J7" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="31" t="s">
+      <c r="K7" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
       <c r="N7" t="b">
         <v>1</v>
       </c>
@@ -1908,14 +1907,14 @@
       <c r="I8" t="s">
         <v>56</v>
       </c>
-      <c r="J8" s="30" t="s">
+      <c r="J8" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="K8" s="31" t="s">
+      <c r="K8" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
       <c r="N8" t="b">
         <v>1</v>
       </c>
@@ -1934,14 +1933,14 @@
       <c r="I9" t="s">
         <v>61</v>
       </c>
-      <c r="J9" s="30" t="s">
+      <c r="J9" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="31" t="s">
+      <c r="K9" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
       <c r="N9" t="b">
         <v>1</v>
       </c>
@@ -1970,11 +1969,11 @@
       <c r="J10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K10" s="33" t="s">
+      <c r="K10" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
       <c r="N10" s="20" t="b">
         <v>1</v>
       </c>
@@ -2003,11 +2002,11 @@
       <c r="J11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="K11" s="35" t="s">
+      <c r="K11" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
       <c r="N11" s="21" t="b">
         <v>1</v>
       </c>
@@ -2034,11 +2033,11 @@
       <c r="J12" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K12" s="35" t="s">
+      <c r="K12" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
       <c r="O12" s="21" t="b">
         <v>1</v>
       </c>
@@ -2065,11 +2064,11 @@
       <c r="J13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K13" s="35" t="s">
+      <c r="K13" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
       <c r="O13" s="21" t="b">
         <v>1</v>
       </c>
@@ -2096,11 +2095,11 @@
       <c r="J14" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="K14" s="35" t="s">
+      <c r="K14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
       <c r="O14" s="21" t="b">
         <v>1</v>
       </c>
@@ -2129,11 +2128,11 @@
       <c r="J15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K15" s="37" t="s">
+      <c r="K15" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
       <c r="N15" s="22" t="b">
         <v>1</v>
       </c>
@@ -2143,27 +2142,27 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="1"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1"/>
